--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91DB9B7-0450-2B40-B3A0-FDD0C938340D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969F5B63-7087-E94F-87E4-09FCA625697C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
+    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="curriculo" sheetId="2" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="856">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2707,6 +2707,15 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1rwS6apoz_umZ361NzOLeCHaJ3FiT3Xsx</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rh76_GoMZUO3JtbOpbvqKciubuzyKNnv</t>
+  </si>
+  <si>
+    <t>10.21203/rs.3.rs-8920372/v1</t>
+  </si>
+  <si>
+    <t>Andrelino, P. C. L., Rodrigues, E., Oliveira, L. A. S., &amp; Ferreira, A. S. (2026). Functional Status and Rehabilitation Barriers in Adults of Working Age After Stroke: A Cross-Sectional Study. Springer Science and Business Media LLC. https://doi.org/10.21203/rs.3.rs-8920372/v1</t>
   </si>
 </sst>
 </file>
@@ -5983,7 +5992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA81A273-40D1-C043-B92A-150693AC55EB}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -6058,6 +6067,17 @@
         <v>844</v>
       </c>
     </row>
+    <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>854</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
@@ -6068,9 +6088,10 @@
     <hyperlink ref="B4" r:id="rId3" xr:uid="{CA1C0CE0-5F21-B843-BBE3-91B53DFACE57}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{2C94C806-EACF-6D44-9C7E-30C52899A3FD}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{263172B8-675C-694E-B35C-A9767EC0337B}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{34713DE2-3C26-064D-8A48-31183CD24318}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969F5B63-7087-E94F-87E4-09FCA625697C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9407E1E4-1778-4945-A5B9-E973561279FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
+    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="4" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="curriculo" sheetId="2" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="859">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2716,6 +2716,15 @@
   </si>
   <si>
     <t>Andrelino, P. C. L., Rodrigues, E., Oliveira, L. A. S., &amp; Ferreira, A. S. (2026). Functional Status and Rehabilitation Barriers in Adults of Working Age After Stroke: A Cross-Sectional Study. Springer Science and Business Media LLC. https://doi.org/10.21203/rs.3.rs-8920372/v1</t>
+  </si>
+  <si>
+    <t>10.3390/books978-3-7258-6745-5</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jkvYvcX4pRqhzb3BYiND5QcsolI9oaG0</t>
+  </si>
+  <si>
+    <t>Symmetry Application in Motor Control in Sports and Rehabilitation (2026). Edited by Arthur de Sá Ferreira &amp; Fabio Vieira dos Anjos</t>
   </si>
 </sst>
 </file>
@@ -6097,7 +6106,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE4DD07-1D2F-4849-A579-59C2F2CCD7DE}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -6139,13 +6148,25 @@
         <v>756</v>
       </c>
     </row>
+    <row r="4" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>858</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>856</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{A14EBD9A-F7A3-2249-972A-30351CA7CBFB}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{F0FF63D1-F8E7-A84A-ADC9-D8854FA383F0}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{D64CC175-1B67-A847-B3BA-9587BDF14D50}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9407E1E4-1778-4945-A5B9-E973561279FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA16172-8369-5A4E-9F85-E5B251604044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="4" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -2724,7 +2724,7 @@
     <t>https://drive.google.com/file/d/1jkvYvcX4pRqhzb3BYiND5QcsolI9oaG0</t>
   </si>
   <si>
-    <t>Symmetry Application in Motor Control in Sports and Rehabilitation (2026). Edited by Arthur de Sá Ferreira &amp; Fabio Vieira dos Anjos</t>
+    <t>Ferreira, A., &amp; dos Anjos, F. V. (Eds.). (2026). Symmetry Application in Motor Control in Sports and Rehabilitation. MDPI. https://doi.org/10.3390/books978-3-7258-6745-5</t>
   </si>
 </sst>
 </file>
@@ -2833,7 +2833,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2911,6 +2911,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6148,8 +6151,8 @@
         <v>756</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A4" s="27" t="s">
         <v>858</v>
       </c>
       <c r="B4" s="7" t="s">

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/CienciaComRConsultoria/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA16172-8369-5A4E-9F85-E5B251604044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B59E23-1F06-414D-AEF8-3042EDCA6AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="4" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
+    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="curriculo" sheetId="2" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="862">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2725,6 +2725,15 @@
   </si>
   <si>
     <t>Ferreira, A., &amp; dos Anjos, F. V. (Eds.). (2026). Symmetry Application in Motor Control in Sports and Rehabilitation. MDPI. https://doi.org/10.3390/books978-3-7258-6745-5</t>
+  </si>
+  <si>
+    <t>John, R. L., Lemos, T., de Sá Ferreira, A., Imbiriba, L. A., &amp; dos Anjos, F. V. (2026). The Relationship Between Psychological Factors and Postural Performance under Different Biofeedback Conditions. Applied Psychophysiology and Biofeedback. https://doi.org/10.1007/s10484-026-09779-5</t>
+  </si>
+  <si>
+    <t>10.1007/s10484-026-09779-5</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15ucxBnoM81Isfeb891uZ0O5348j30v1S/view</t>
   </si>
 </sst>
 </file>
@@ -3403,7 +3412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C215"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5755,25 +5764,36 @@
         <v>847</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A214" s="22" t="s">
+    <row r="214" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A214" s="27" t="s">
+        <v>859</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="C214" s="27" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A215" s="22" t="s">
         <v>838</v>
       </c>
-      <c r="B214" s="23" t="s">
+      <c r="B215" s="23" t="s">
         <v>840</v>
       </c>
-      <c r="C214" s="22" t="s">
+      <c r="C215" s="22" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A215" s="6" t="s">
+    <row r="216" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A216" s="6" t="s">
         <v>850</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B216" s="7" t="s">
         <v>852</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C216" s="6" t="s">
         <v>851</v>
       </c>
     </row>
@@ -5992,13 +6012,14 @@
     <hyperlink ref="B211" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
     <hyperlink ref="B212" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B214" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B215" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
     <hyperlink ref="B213" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B215" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B216" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B214" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId215"/>
+  <legacyDrawing r:id="rId216"/>
 </worksheet>
 </file>
 
@@ -6152,7 +6173,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="6" t="s">
         <v>858</v>
       </c>
       <c r="B4" s="7" t="s">

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B59E23-1F06-414D-AEF8-3042EDCA6AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF112FEF-CCF6-1D4E-9D04-3B46060E9AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="865">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2337,9 +2337,6 @@
   </si>
   <si>
     <t>10.1080/21679169.2025.2497780</t>
-  </si>
-  <si>
-    <t>Reis, F. J. J., Neves, G. de A., Carvalho, M. B. L. de, Nogueira, L. C., Meziat-Filho, N., Medeiros, F. C., &amp; Sá Ferreira, A. de. (2025). Mapping global research on artificial intelligence in physical therapy: a bibliometric analysis from 1990 to 2023. In European Journal of Physiotherapy (pp. 1–11). Informa UK Limited. https://doi.org/10.1080/21679169.2025.2497780</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/16_pb4XaR4vFWN-TrDv-0RuR5PQK3U0ZT</t>
@@ -2697,9 +2694,6 @@
     <t>https://drive.google.com/file/d/1MAmQfzZPNcZT4dlfY3gCM44XnIk3vtQU</t>
   </si>
   <si>
-    <t>Ferreira, A. de S., &amp; Parisotto, G. (2026). Insights from Ungureanu et al.: interpreting AI-clinician disagreement in ECG diagnostics. Acta Cardiologica, 1–3. https://doi.org/10.1080/00015385.2026.2630134</t>
-  </si>
-  <si>
     <t>Sancho, Alexandre Gomes1,2; Ferreira, Arthur de Sá1,*. Engaging citizen science: Exploring popular participation in scientific projects in rehabilitation. Aging Medicine and Healthcare 17(1):p 53-58, Jan–Mar 2026. | DOI: 10.4103/AMAH.AMH-2024-07-068</t>
   </si>
   <si>
@@ -2734,6 +2728,21 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/15ucxBnoM81Isfeb891uZ0O5348j30v1S/view</t>
+  </si>
+  <si>
+    <t>Ferreira, A. de S., &amp; Parisotto, G. (2026). Insights from Ungureanu et al.: interpreting AI-clinician disagreement in ECG diagnostics. Acta Cardiologica, 81(2), 247–249. https://doi.org/10.1080/00015385.2026.2630134</t>
+  </si>
+  <si>
+    <t>Reis, F. J. J., Neves, G. de A., Carvalho, M. B. L. de, Nogueira, L. C., Meziat-Filho, N., Medeiros, F. C., &amp; Sá Ferreira, A. de. (2025). Mapping global research on artificial intelligence in physical therapy: a bibliometric analysis from 1990 to 2023. European Journal of Physiotherapy, 28(2), 115–125. https://doi.org/10.1080/21679169.2025.2497780</t>
+  </si>
+  <si>
+    <t>Lunkes, L. C., Dias Neto, M. A., Barra, L. F., de Castro, L. R., de Sá Ferreira, A., &amp; Meziat-Filho, N. (2026). Keeping the abdomen relaxed versus contracted during Pilates improves disability slightly and may improve other outcomes in chronic non-specific low back pain: a randomised trial. Journal of Physiotherapy. https://doi.org/10.1016/j.jphys.2026.03.007</t>
+  </si>
+  <si>
+    <t>10.1016/j.jphys.2026.03.007</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/135S0wcpdRSqOnDe67OfVAIQjMVR1liYA</t>
   </si>
 </sst>
 </file>
@@ -2842,7 +2851,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2920,9 +2929,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3412,7 +3418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5513,51 +5519,51 @@
     </row>
     <row r="191" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="B191" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="B191" s="7" t="s">
-        <v>843</v>
-      </c>
       <c r="C191" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B192" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="C192" s="6" t="s">
         <v>822</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B193" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="C193" s="6" t="s">
         <v>835</v>
-      </c>
-      <c r="C193" s="6" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="B194" s="7" t="s">
         <v>750</v>
       </c>
-      <c r="B194" s="7" t="s">
-        <v>751</v>
-      </c>
       <c r="C194" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>695</v>
@@ -5568,13 +5574,13 @@
     </row>
     <row r="196" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B196" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="C196" s="6" t="s">
         <v>744</v>
-      </c>
-      <c r="C196" s="6" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="102" x14ac:dyDescent="0.2">
@@ -5590,29 +5596,29 @@
     </row>
     <row r="198" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A198" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>715</v>
@@ -5634,35 +5640,35 @@
     </row>
     <row r="202" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="B202" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>737</v>
-      </c>
       <c r="C202" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B203" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="B203" s="9" t="s">
-        <v>754</v>
-      </c>
       <c r="C203" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B204" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="C204" s="6" t="s">
         <v>761</v>
-      </c>
-      <c r="C204" s="6" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="119" x14ac:dyDescent="0.2">
@@ -5678,21 +5684,21 @@
     </row>
     <row r="206" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B206" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>760</v>
-      </c>
       <c r="C206" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A207" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="B207" s="9" t="s">
         <v>733</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>734</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>732</v>
@@ -5722,79 +5728,90 @@
     </row>
     <row r="210" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A210" s="25" t="s">
+        <v>826</v>
+      </c>
+      <c r="B210" s="26" t="s">
         <v>827</v>
       </c>
-      <c r="B210" s="26" t="s">
-        <v>828</v>
-      </c>
       <c r="C210" s="25" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A211" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="B211" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="B211" s="7" t="s">
-        <v>831</v>
-      </c>
       <c r="C211" s="6" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="B212" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="B212" s="7" t="s">
-        <v>834</v>
-      </c>
       <c r="C212" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A213" s="22" t="s">
+      <c r="A213" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A214" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A215" s="22" t="s">
+        <v>862</v>
+      </c>
+      <c r="B215" s="23" t="s">
+        <v>864</v>
+      </c>
+      <c r="C215" s="22" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A216" s="22" t="s">
+        <v>837</v>
+      </c>
+      <c r="B216" s="23" t="s">
+        <v>839</v>
+      </c>
+      <c r="C216" s="22" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A217" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C217" s="6" t="s">
         <v>849</v>
-      </c>
-      <c r="B213" s="23" t="s">
-        <v>848</v>
-      </c>
-      <c r="C213" s="22" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A214" s="27" t="s">
-        <v>859</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>861</v>
-      </c>
-      <c r="C214" s="27" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A215" s="22" t="s">
-        <v>838</v>
-      </c>
-      <c r="B215" s="23" t="s">
-        <v>840</v>
-      </c>
-      <c r="C215" s="22" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A216" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="B216" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="C216" s="6" t="s">
-        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -6012,14 +6029,15 @@
     <hyperlink ref="B211" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
     <hyperlink ref="B212" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B215" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B216" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
     <hyperlink ref="B213" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B216" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B217" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
     <hyperlink ref="B214" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B215" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId216"/>
+  <legacyDrawing r:id="rId217"/>
 </worksheet>
 </file>
 
@@ -6080,35 +6098,35 @@
     </row>
     <row r="5" spans="1:3" s="14" customFormat="1" ht="154" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>784</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>785</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>786</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -6163,24 +6181,24 @@
     </row>
     <row r="3" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>755</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -6652,79 +6670,79 @@
     </row>
     <row r="31" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A34" s="22" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -6867,10 +6885,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>787</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>788</v>
       </c>
       <c r="C9" s="24"/>
     </row>
@@ -6917,123 +6935,123 @@
     </row>
     <row r="2" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>789</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>792</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>793</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>795</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>796</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>799</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>801</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>802</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>804</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>805</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>808</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>811</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>814</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>817</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>820</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>821</v>
       </c>
     </row>
   </sheetData>

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF112FEF-CCF6-1D4E-9D04-3B46060E9AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B440663-F205-9441-80B9-CEDB1A275B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="868">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2743,6 +2743,15 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/135S0wcpdRSqOnDe67OfVAIQjMVR1liYA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1muhPCJnvrvw3P07IJ1KbW8BzcDLSaLqo</t>
+  </si>
+  <si>
+    <t>10.1016/j.ijosm.2026.100830</t>
+  </si>
+  <si>
+    <t>Curi, A. C. C., Ferreira, A. P. A., Nogueira, L. A. C., Meziat Filho, N., &amp; de Sá Ferreira, A. (2026). FATIGUE IN LONG COVID: AN EXPLORATORY PRAGMATIC RANDOMIZED TRIAL OF OSTEOPATHIC CARE PLUS PHYSICAL THERAPY VERSUS PHYSICAL THERAPY ALONE. International Journal of Osteopathic Medicine, 100830. https://doi.org/10.1016/j.ijosm.2026.100830</t>
   </si>
 </sst>
 </file>
@@ -3418,7 +3427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5748,69 +5757,80 @@
         <v>828</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A212" s="6" t="s">
+    <row r="212" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A212" s="22" t="s">
+        <v>867</v>
+      </c>
+      <c r="B212" s="23" t="s">
+        <v>865</v>
+      </c>
+      <c r="C212" s="22" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A213" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B213" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C213" s="6" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A213" s="6" t="s">
+    <row r="214" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A214" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="B214" s="9" t="s">
         <v>847</v>
       </c>
-      <c r="C213" s="6" t="s">
+      <c r="C214" s="6" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A214" s="6" t="s">
+    <row r="215" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A215" s="6" t="s">
         <v>857</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B215" s="9" t="s">
         <v>859</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C215" s="6" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A215" s="22" t="s">
+    <row r="216" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A216" s="22" t="s">
         <v>862</v>
       </c>
-      <c r="B215" s="23" t="s">
+      <c r="B216" s="23" t="s">
         <v>864</v>
       </c>
-      <c r="C215" s="22" t="s">
+      <c r="C216" s="22" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A216" s="22" t="s">
+    <row r="217" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A217" s="22" t="s">
         <v>837</v>
       </c>
-      <c r="B216" s="23" t="s">
+      <c r="B217" s="23" t="s">
         <v>839</v>
       </c>
-      <c r="C216" s="22" t="s">
+      <c r="C217" s="22" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A217" s="6" t="s">
+    <row r="218" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A218" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B218" s="7" t="s">
         <v>850</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C218" s="6" t="s">
         <v>849</v>
       </c>
     </row>
@@ -6027,17 +6047,18 @@
     <hyperlink ref="B192" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
     <hyperlink ref="B210" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
     <hyperlink ref="B211" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
-    <hyperlink ref="B212" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
+    <hyperlink ref="B213" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B216" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B217" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B213" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B217" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B214" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B215" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B214" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B218" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B215" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B216" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B212" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId217"/>
+  <legacyDrawing r:id="rId218"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B440663-F205-9441-80B9-CEDB1A275B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFC7D84-6BDA-EA4D-9FB4-F1327D9E087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="871">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2163,9 +2163,6 @@
   </si>
   <si>
     <t>10.1016/j.jbmt.2024.12.016</t>
-  </si>
-  <si>
-    <t>Resende, P. A., Tavares Correia, I. M., de Sá Ferreira, A., Meziat-Filho, N., &amp; Lunkes, L. C. (2024). NECK PAIN AND TEXT NECK USING HILL’S CRITERIA OF CAUSATION: A SCOPING REVIEW. In Journal of Bodywork and Movement Therapies. Elsevier BV. https://doi.org/10.1016/j.jbmt.2024.12.016</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1A2SnqSYMEohq4Y68BbvLOJW7D8MRTvMg</t>
@@ -2736,9 +2733,6 @@
     <t>Reis, F. J. J., Neves, G. de A., Carvalho, M. B. L. de, Nogueira, L. C., Meziat-Filho, N., Medeiros, F. C., &amp; Sá Ferreira, A. de. (2025). Mapping global research on artificial intelligence in physical therapy: a bibliometric analysis from 1990 to 2023. European Journal of Physiotherapy, 28(2), 115–125. https://doi.org/10.1080/21679169.2025.2497780</t>
   </si>
   <si>
-    <t>Lunkes, L. C., Dias Neto, M. A., Barra, L. F., de Castro, L. R., de Sá Ferreira, A., &amp; Meziat-Filho, N. (2026). Keeping the abdomen relaxed versus contracted during Pilates improves disability slightly and may improve other outcomes in chronic non-specific low back pain: a randomised trial. Journal of Physiotherapy. https://doi.org/10.1016/j.jphys.2026.03.007</t>
-  </si>
-  <si>
     <t>10.1016/j.jphys.2026.03.007</t>
   </si>
   <si>
@@ -2752,6 +2746,21 @@
   </si>
   <si>
     <t>Curi, A. C. C., Ferreira, A. P. A., Nogueira, L. A. C., Meziat Filho, N., &amp; de Sá Ferreira, A. (2026). FATIGUE IN LONG COVID: AN EXPLORATORY PRAGMATIC RANDOMIZED TRIAL OF OSTEOPATHIC CARE PLUS PHYSICAL THERAPY VERSUS PHYSICAL THERAPY ALONE. International Journal of Osteopathic Medicine, 100830. https://doi.org/10.1016/j.ijosm.2026.100830</t>
+  </si>
+  <si>
+    <t>Lunkes, L. C., Dias Neto, M. A., Barra, L. F., de Castro, L. R., de Sá Ferreira, A., &amp; Meziat-Filho, N. (2026). Keeping the abdomen relaxed versus contracted during Pilates improves disability slightly and may improve other outcomes in chronic non-specific low back pain: a randomised trial. Journal of Physiotherapy, 72(2), 116–121. https://doi.org/10.1016/j.jphys.2026.03.007</t>
+  </si>
+  <si>
+    <t>Resende, P. A., Tavares Correia, I. M., de Sá Ferreira, A., Meziat-Filho, N., &amp; Lunkes, L. C. (2025). Neck pain and text neck using Hill’s criteria of causation: A scoping review. Journal of Bodywork and Movement Therapies, 42, 132–138. https://doi.org/10.1016/j.jbmt.2024.12.016</t>
+  </si>
+  <si>
+    <t>Arulsingh, W., de Sá Ferreira, A., Kandakurti, P. K., &amp; Patil, S. S. (2026). C5–C6 and thoracic spine mobilization with postural correction exercise compared with conventional therapy in patients with adhesive capsulitis: a two-group, parallel-arm, single-blinded, randomized clinical trial—study protocol. Trials. https://doi.org/10.1186/s13063-026-09690-8</t>
+  </si>
+  <si>
+    <t>10.1186/s13063-026-09690-8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pZ47Q-kKC1ie7FDxqS8bsenF1t-hn7DI</t>
   </si>
 </sst>
 </file>
@@ -2849,8 +2858,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2860,7 +2871,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2938,6 +2949,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3427,7 +3441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C218"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -3623,7 +3637,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>65</v>
       </c>
@@ -3656,7 +3670,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>86</v>
       </c>
@@ -3788,7 +3802,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>107</v>
       </c>
@@ -5440,13 +5454,13 @@
     </row>
     <row r="183" spans="1:3" ht="204" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B183" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>711</v>
-      </c>
       <c r="C183" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -5506,186 +5520,186 @@
     </row>
     <row r="189" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="B189" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="B189" s="7" t="s">
-        <v>698</v>
-      </c>
       <c r="C189" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A190" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C190" s="6" t="s">
         <v>699</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>701</v>
-      </c>
-      <c r="C190" s="6" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="B191" s="7" t="s">
         <v>841</v>
       </c>
-      <c r="B191" s="7" t="s">
-        <v>842</v>
-      </c>
       <c r="C191" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B192" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="C192" s="6" t="s">
         <v>821</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B193" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="C193" s="6" t="s">
         <v>834</v>
-      </c>
-      <c r="C193" s="6" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B194" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="B194" s="7" t="s">
-        <v>750</v>
-      </c>
       <c r="C194" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B196" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="C196" s="6" t="s">
         <v>743</v>
-      </c>
-      <c r="C196" s="6" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="C197" s="6" t="s">
         <v>729</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A198" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A201" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="B202" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>736</v>
-      </c>
       <c r="C202" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="B203" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="B203" s="9" t="s">
-        <v>753</v>
-      </c>
       <c r="C203" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B204" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="C204" s="6" t="s">
         <v>760</v>
-      </c>
-      <c r="C204" s="6" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="B205" s="9" t="s">
         <v>675</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>676</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>674</v>
@@ -5693,145 +5707,156 @@
     </row>
     <row r="206" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="B206" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>759</v>
-      </c>
       <c r="C206" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A207" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A208" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A209" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A210" s="25" t="s">
+        <v>825</v>
+      </c>
+      <c r="B210" s="26" t="s">
         <v>826</v>
       </c>
-      <c r="B210" s="26" t="s">
+      <c r="C210" s="25" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A211" s="27" t="s">
+        <v>868</v>
+      </c>
+      <c r="B211" s="17" t="s">
+        <v>870</v>
+      </c>
+      <c r="C211" s="27" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A212" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="C212" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="C210" s="25" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A211" s="6" t="s">
-        <v>829</v>
-      </c>
-      <c r="B211" s="7" t="s">
+    </row>
+    <row r="213" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A213" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="B213" s="23" t="s">
+        <v>863</v>
+      </c>
+      <c r="C213" s="22" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A214" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="C214" s="6" t="s">
         <v>830</v>
       </c>
-      <c r="C211" s="6" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A212" s="22" t="s">
-        <v>867</v>
-      </c>
-      <c r="B212" s="23" t="s">
-        <v>865</v>
-      </c>
-      <c r="C212" s="22" t="s">
+    </row>
+    <row r="215" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A215" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A216" s="6" t="s">
+        <v>856</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A217" s="6" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A213" s="6" t="s">
-        <v>832</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="C213" s="6" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A214" s="6" t="s">
-        <v>860</v>
-      </c>
-      <c r="B214" s="9" t="s">
+      <c r="B217" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A218" s="22" t="s">
+        <v>836</v>
+      </c>
+      <c r="B218" s="23" t="s">
+        <v>838</v>
+      </c>
+      <c r="C218" s="22" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A219" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="C214" s="6" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A215" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>859</v>
-      </c>
-      <c r="C215" s="6" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A216" s="22" t="s">
-        <v>862</v>
-      </c>
-      <c r="B216" s="23" t="s">
-        <v>864</v>
-      </c>
-      <c r="C216" s="22" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A217" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="B217" s="23" t="s">
-        <v>839</v>
-      </c>
-      <c r="C217" s="22" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A218" s="6" t="s">
+      <c r="B219" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="C219" s="6" t="s">
         <v>848</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>850</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -6046,19 +6071,20 @@
     <hyperlink ref="B204" r:id="rId205" xr:uid="{5A78EF2F-315D-0248-82E7-3837C642D8EE}"/>
     <hyperlink ref="B192" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
     <hyperlink ref="B210" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
-    <hyperlink ref="B211" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
-    <hyperlink ref="B213" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
+    <hyperlink ref="B212" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
+    <hyperlink ref="B214" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B217" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B218" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B214" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B218" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B215" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B216" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
-    <hyperlink ref="B212" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B215" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B219" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B216" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B217" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B213" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B211" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId218"/>
+  <legacyDrawing r:id="rId219"/>
 </worksheet>
 </file>
 
@@ -6086,68 +6112,68 @@
     </row>
     <row r="2" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>689</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="256" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>688</v>
-      </c>
       <c r="C3" s="12" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>704</v>
-      </c>
       <c r="C4" s="6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="14" customFormat="1" ht="154" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>783</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>784</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>785</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>851</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -6191,35 +6217,35 @@
     </row>
     <row r="2" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>683</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>754</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -6335,35 +6361,35 @@
     </row>
     <row r="11" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>718</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -6623,26 +6649,26 @@
     </row>
     <row r="24" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>719</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>721</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>723</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="153" x14ac:dyDescent="0.2">
@@ -6691,79 +6717,79 @@
     </row>
     <row r="31" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A34" s="22" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -6895,21 +6921,21 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>727</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>786</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>787</v>
       </c>
       <c r="C9" s="24"/>
     </row>
@@ -6956,123 +6982,123 @@
     </row>
     <row r="2" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>788</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>790</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>791</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>792</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>794</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>795</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>797</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>798</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>800</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>801</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>803</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>804</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>807</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>809</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>810</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>813</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>816</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>819</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>820</v>
       </c>
     </row>
   </sheetData>

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFC7D84-6BDA-EA4D-9FB4-F1327D9E087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95B25F-E9C1-7946-A186-B1B74E3784F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="874">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2761,6 +2761,17 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1pZ47Q-kKC1ie7FDxqS8bsenF1t-hn7DI</t>
+  </si>
+  <si>
+    <t>Abrahão PN, Filho NM, Rodrigues E, Pinto TP, Ferreira AS. ‘Seeing pain differently’: the
+impact of physiotherapists’ attitudes and treatment beliefs on postural assessment in neck pain – an eye-tracking
+study. Adv Rehab. 2026; 40(1): 16-35. doi: 10.2478/advrehab-2026-0002</t>
+  </si>
+  <si>
+    <t>10.2478/advrehab-2026-0002</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1v5neQlRlI4WXmq-yvhDJ9WoOup1dDQPI</t>
   </si>
 </sst>
 </file>
@@ -2871,7 +2882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2952,6 +2963,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3441,7 +3455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C219"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5760,102 +5774,113 @@
         <v>824</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A211" s="27" t="s">
+        <v>871</v>
+      </c>
+      <c r="B211" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="C211" s="27" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A212" s="22" t="s">
         <v>868</v>
       </c>
-      <c r="B211" s="17" t="s">
+      <c r="B212" s="28" t="s">
         <v>870</v>
       </c>
-      <c r="C211" s="27" t="s">
+      <c r="C212" s="22" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A212" s="6" t="s">
+    <row r="213" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A213" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B213" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C213" s="6" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A213" s="22" t="s">
+    <row r="214" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A214" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="B213" s="23" t="s">
+      <c r="B214" s="9" t="s">
         <v>863</v>
       </c>
-      <c r="C213" s="22" t="s">
+      <c r="C214" s="6" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A214" s="6" t="s">
+    <row r="215" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A215" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B215" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C215" s="6" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A215" s="6" t="s">
+    <row r="216" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A216" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B216" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C216" s="6" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A216" s="6" t="s">
+    <row r="217" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A217" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="B216" s="9" t="s">
+      <c r="B217" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C217" s="6" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A217" s="6" t="s">
+    <row r="218" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A218" s="6" t="s">
         <v>866</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B218" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C218" s="6" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A218" s="22" t="s">
+    <row r="219" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A219" s="22" t="s">
         <v>836</v>
       </c>
-      <c r="B218" s="23" t="s">
+      <c r="B219" s="23" t="s">
         <v>838</v>
       </c>
-      <c r="C218" s="22" t="s">
+      <c r="C219" s="22" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A219" s="6" t="s">
+    <row r="220" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A220" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="B219" s="7" t="s">
+      <c r="B220" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="C219" s="6" t="s">
+      <c r="C220" s="6" t="s">
         <v>848</v>
       </c>
     </row>
@@ -6071,20 +6096,21 @@
     <hyperlink ref="B204" r:id="rId205" xr:uid="{5A78EF2F-315D-0248-82E7-3837C642D8EE}"/>
     <hyperlink ref="B192" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
     <hyperlink ref="B210" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
-    <hyperlink ref="B212" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
-    <hyperlink ref="B214" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
+    <hyperlink ref="B213" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
+    <hyperlink ref="B215" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B218" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B219" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B215" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B219" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B216" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B217" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
-    <hyperlink ref="B213" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
-    <hyperlink ref="B211" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
+    <hyperlink ref="B216" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B220" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B217" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B218" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B214" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B212" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
+    <hyperlink ref="B211" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId219"/>
+  <legacyDrawing r:id="rId220"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95B25F-E9C1-7946-A186-B1B74E3784F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB1A75D-4128-914C-96AD-60A95FEFD820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="880">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2754,9 +2754,6 @@
     <t>Resende, P. A., Tavares Correia, I. M., de Sá Ferreira, A., Meziat-Filho, N., &amp; Lunkes, L. C. (2025). Neck pain and text neck using Hill’s criteria of causation: A scoping review. Journal of Bodywork and Movement Therapies, 42, 132–138. https://doi.org/10.1016/j.jbmt.2024.12.016</t>
   </si>
   <si>
-    <t>Arulsingh, W., de Sá Ferreira, A., Kandakurti, P. K., &amp; Patil, S. S. (2026). C5–C6 and thoracic spine mobilization with postural correction exercise compared with conventional therapy in patients with adhesive capsulitis: a two-group, parallel-arm, single-blinded, randomized clinical trial—study protocol. Trials. https://doi.org/10.1186/s13063-026-09690-8</t>
-  </si>
-  <si>
     <t>10.1186/s13063-026-09690-8</t>
   </si>
   <si>
@@ -2772,6 +2769,27 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1v5neQlRlI4WXmq-yvhDJ9WoOup1dDQPI</t>
+  </si>
+  <si>
+    <t>10.1016/j.jorep.2026.101049</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GLlEoQ8t7JgNqQUPY2QSvdwkHOSbiuhA</t>
+  </si>
+  <si>
+    <t>Arulsingh, W., de Sá Ferreira, A., Kandakurti, P.K. et al. C5–C6 and thoracic spine mobilization with postural correction exercise compared with conventional therapy in patients with adhesive capsulitis: a two-group, parallel-arm, single-blinded, randomized clinical trial—study protocol. Trials 27, 378 (2026). https://doi.org/10.1186/s13063-026-09690-8</t>
+  </si>
+  <si>
+    <t>Ribeiro, R. de S. T., Anjos, F. V. dos, Jesus, I. R. T. de, Monteiro, E. R., &amp; Ferreira, A. de S. (2026). Immediate effects of self-massage compared to static stretching on neuromuscular and functional performance of physically active healthy adults: A crossover study. Journal of Orthopaedic Reports, 101049. https://doi.org/10.1016/j.jorep.2026.101049</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bvClSoEZjVttegI9SH3ZhPh-NTAwBHqJ</t>
+  </si>
+  <si>
+    <t>10.63231/2595-0118.202670-en</t>
+  </si>
+  <si>
+    <t>Ramos, A. L. C. O., Silva, J. E. das M., Ferreira, A. de S., &amp; Lunkes, L. C. (2026). Health locus of control and its relationship with kinesiophobia, disability, and prognosis in chronic low back pain. Brazilian Journal of Pain, 9, e202670. https://doi.org/10.63231/2595-0118.202670-en</t>
   </si>
 </sst>
 </file>
@@ -2882,7 +2900,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2962,10 +2980,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3455,7 +3470,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C222"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -3651,7 +3666,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>65</v>
       </c>
@@ -3684,7 +3699,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>86</v>
       </c>
@@ -3816,7 +3831,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>107</v>
       </c>
@@ -5775,25 +5790,25 @@
       </c>
     </row>
     <row r="211" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A211" s="27" t="s">
+      <c r="A211" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="B211" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="C211" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="B211" s="17" t="s">
-        <v>873</v>
-      </c>
-      <c r="C211" s="27" t="s">
-        <v>872</v>
-      </c>
     </row>
     <row r="212" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A212" s="22" t="s">
+      <c r="A212" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="B212" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="C212" s="6" t="s">
         <v>868</v>
-      </c>
-      <c r="B212" s="28" t="s">
-        <v>870</v>
-      </c>
-      <c r="C212" s="22" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="153" x14ac:dyDescent="0.2">
@@ -5874,13 +5889,35 @@
       </c>
     </row>
     <row r="220" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A220" s="6" t="s">
+      <c r="A220" s="27" t="s">
+        <v>879</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="C220" s="27" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A221" s="22" t="s">
+        <v>876</v>
+      </c>
+      <c r="B221" s="23" t="s">
+        <v>874</v>
+      </c>
+      <c r="C221" s="22" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A222" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B222" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="C220" s="6" t="s">
+      <c r="C222" s="6" t="s">
         <v>848</v>
       </c>
     </row>
@@ -6102,15 +6139,17 @@
     <hyperlink ref="B219" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
     <hyperlink ref="B216" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B220" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B222" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
     <hyperlink ref="B217" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
     <hyperlink ref="B218" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
     <hyperlink ref="B214" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
     <hyperlink ref="B212" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
     <hyperlink ref="B211" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
+    <hyperlink ref="B221" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
+    <hyperlink ref="B220" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId220"/>
+  <legacyDrawing r:id="rId222"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB1A75D-4128-914C-96AD-60A95FEFD820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B792260C-3241-7C48-B95B-51A211EDD315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="889">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2790,6 +2790,33 @@
   </si>
   <si>
     <t>Ramos, A. L. C. O., Silva, J. E. das M., Ferreira, A. de S., &amp; Lunkes, L. C. (2026). Health locus of control and its relationship with kinesiophobia, disability, and prognosis in chronic low back pain. Brazilian Journal of Pain, 9, e202670. https://doi.org/10.63231/2595-0118.202670-en</t>
+  </si>
+  <si>
+    <t>Albuquerque, F., Ferreira, A. S., &amp; Lemos, T. (2026). Posturographic assessment of shoulder complex stability in swimmers during Upper-Quarter Y Balance Test: cross-sectional study in young athletes, regarding handedness. Muscles, Ligaments and Tendons Journal, 16. https://doi.org/10.32098/mltj_2026_7106</t>
+  </si>
+  <si>
+    <t>10.32098/mltj_2026_7106</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jz-WI11D1a-kky2T5GxSutK1pz2hOqBN</t>
+  </si>
+  <si>
+    <t>Kong CYA, Amaravadi SK, Costa J et al. Effect of high-intensity interval training (HIIT) versus moderate-intensity continuous training (MICT) on insulin sensitivity in participants with type 2 diabetes mellitus (T2DM): A systematic review and meta-analysis of randomised controlled trials [version 1; peer review: awaiting peer review]. F1000Research 2026, 15:836 (https://doi.org/10.12688/f1000research.180073.1)</t>
+  </si>
+  <si>
+    <t>10.12688/f1000research.180073.1</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13NOsW0m7_IT4KMKmhtP7HdguAJDvM0hJ</t>
+  </si>
+  <si>
+    <t>10.63231/2595-0118.202673-en</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XBy21oPU8HveQbSfWq0GQXBIikv2JLGZ</t>
+  </si>
+  <si>
+    <t>Carvalho, L. C. de, Ferreira, A. de S., da-Silva, G. C., &amp; Lunkes, L. C. (2026). Association between pain locus of control and fall risk in older adults with chronic pain: community-based cross-sectional study. Brazilian Journal of Pain, 9, e202673. https://doi.org/10.63231/2595-0118.202673-en</t>
   </si>
 </sst>
 </file>
@@ -3470,7 +3497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C222"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5800,124 +5827,157 @@
         <v>871</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="B212" s="17" t="s">
+        <v>882</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A213" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="B212" s="20" t="s">
+      <c r="B213" s="20" t="s">
         <v>869</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C213" s="6" t="s">
         <v>868</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A213" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="C213" s="6" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A215" s="27" t="s">
+        <v>888</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="C215" s="27" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A216" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B216" s="9" t="s">
         <v>863</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C216" s="6" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A215" s="6" t="s">
+    <row r="217" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A217" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B217" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C217" s="6" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A216" s="6" t="s">
+    <row r="218" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A218" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="B216" s="9" t="s">
+      <c r="B218" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C218" s="6" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A217" s="6" t="s">
+    <row r="219" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A219" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B219" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C219" s="6" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A218" s="6" t="s">
+    <row r="220" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A220" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A221" s="6" t="s">
         <v>866</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B221" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="C218" s="6" t="s">
+      <c r="C221" s="6" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A219" s="22" t="s">
+    <row r="222" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A222" s="22" t="s">
         <v>836</v>
       </c>
-      <c r="B219" s="23" t="s">
+      <c r="B222" s="23" t="s">
         <v>838</v>
       </c>
-      <c r="C219" s="22" t="s">
+      <c r="C222" s="22" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A220" s="27" t="s">
+    <row r="223" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A223" s="6" t="s">
         <v>879</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="B223" s="9" t="s">
         <v>877</v>
       </c>
-      <c r="C220" s="27" t="s">
+      <c r="C223" s="6" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A221" s="22" t="s">
+    <row r="224" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A224" s="22" t="s">
         <v>876</v>
       </c>
-      <c r="B221" s="23" t="s">
+      <c r="B224" s="23" t="s">
         <v>874</v>
       </c>
-      <c r="C221" s="22" t="s">
+      <c r="C224" s="22" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A222" s="6" t="s">
+    <row r="225" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A225" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B225" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="C222" s="6" t="s">
+      <c r="C225" s="6" t="s">
         <v>848</v>
       </c>
     </row>
@@ -6133,23 +6193,26 @@
     <hyperlink ref="B204" r:id="rId205" xr:uid="{5A78EF2F-315D-0248-82E7-3837C642D8EE}"/>
     <hyperlink ref="B192" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
     <hyperlink ref="B210" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
-    <hyperlink ref="B213" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
-    <hyperlink ref="B215" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
+    <hyperlink ref="B214" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
+    <hyperlink ref="B217" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B219" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B222" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B216" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B222" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B217" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B218" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
-    <hyperlink ref="B214" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
-    <hyperlink ref="B212" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
+    <hyperlink ref="B218" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B225" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B219" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B221" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B216" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B213" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
     <hyperlink ref="B211" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
-    <hyperlink ref="B221" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
-    <hyperlink ref="B220" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
+    <hyperlink ref="B224" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
+    <hyperlink ref="B223" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
+    <hyperlink ref="B212" r:id="rId222" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
+    <hyperlink ref="B220" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
+    <hyperlink ref="B215" r:id="rId224" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId222"/>
+  <legacyDrawing r:id="rId225"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B792260C-3241-7C48-B95B-51A211EDD315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730E7546-DA03-4146-8A40-B195F3E6983E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="892">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2817,6 +2817,15 @@
   </si>
   <si>
     <t>Carvalho, L. C. de, Ferreira, A. de S., da-Silva, G. C., &amp; Lunkes, L. C. (2026). Association between pain locus of control and fall risk in older adults with chronic pain: community-based cross-sectional study. Brazilian Journal of Pain, 9, e202673. https://doi.org/10.63231/2595-0118.202673-en</t>
+  </si>
+  <si>
+    <t>Albuquerque, F., Sá Ferreira, A., &amp; Lemos, T. (2026). Shoulder pain and disability predict clinical outcomes better than biomechanical and functional measures in young swimmers: a prospective cohort study. Revista Andaluza de Medicina Del Deporte, 18(4). https://doi.org/10.33155/ramd.v18i4.1246</t>
+  </si>
+  <si>
+    <t>10.33155/ramd.v18i4.1246</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12VaPnB9xKA3ooN9KcUKhJYD2hwf3Ikv6</t>
   </si>
 </sst>
 </file>
@@ -2927,7 +2936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3005,9 +3014,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3497,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C226"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5596,388 +5602,399 @@
         <v>699</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A192" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B192" s="7" t="s">
         <v>841</v>
       </c>
-      <c r="C191" s="6" t="s">
+      <c r="C192" s="6" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A192" s="6" t="s">
+    <row r="193" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A193" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B193" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="C192" s="6" t="s">
+      <c r="C193" s="6" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A193" s="6" t="s">
+    <row r="194" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A194" s="6" t="s">
         <v>835</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B194" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="C194" s="6" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A194" s="6" t="s">
+    <row r="195" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A195" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B195" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="C194" s="6" t="s">
+      <c r="C195" s="6" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A195" s="6" t="s">
+    <row r="196" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A196" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B196" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="C195" s="6" t="s">
+      <c r="C196" s="6" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A196" s="6" t="s">
+    <row r="197" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A197" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="B196" s="9" t="s">
+      <c r="B197" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="C196" s="6" t="s">
+      <c r="C197" s="6" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A197" s="6" t="s">
+    <row r="198" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A198" s="6" t="s">
         <v>728</v>
       </c>
-      <c r="B197" s="9" t="s">
+      <c r="B198" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="C197" s="6" t="s">
+      <c r="C198" s="6" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A198" s="6" t="s">
+    <row r="199" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A199" s="6" t="s">
         <v>738</v>
       </c>
-      <c r="B198" s="9" t="s">
+      <c r="B199" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="C198" s="6" t="s">
+      <c r="C199" s="6" t="s">
         <v>736</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A199" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="C199" s="6" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A201" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="B200" s="9" t="s">
+      <c r="B201" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="C200" s="6" t="s">
+      <c r="C201" s="6" t="s">
         <v>713</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A201" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="C201" s="6" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A203" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="B202" s="9" t="s">
+      <c r="B203" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="C202" s="6" t="s">
+      <c r="C203" s="6" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A203" s="6" t="s">
+    <row r="204" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A204" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="B203" s="9" t="s">
+      <c r="B204" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="C203" s="6" t="s">
+      <c r="C204" s="6" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A204" s="6" t="s">
+    <row r="205" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A205" s="6" t="s">
         <v>823</v>
       </c>
-      <c r="B204" s="9" t="s">
+      <c r="B205" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="C204" s="6" t="s">
+      <c r="C205" s="6" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A205" s="6" t="s">
+    <row r="206" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A206" s="6" t="s">
         <v>867</v>
       </c>
-      <c r="B205" s="9" t="s">
+      <c r="B206" s="9" t="s">
         <v>675</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C206" s="6" t="s">
         <v>674</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A206" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="C206" s="6" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A207" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A208" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="B207" s="9" t="s">
+      <c r="B208" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="C207" s="6" t="s">
+      <c r="C208" s="6" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="187" x14ac:dyDescent="0.2">
-      <c r="A208" s="6" t="s">
+    <row r="209" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="A209" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="B208" s="9" t="s">
+      <c r="B209" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="C208" s="6" t="s">
+      <c r="C209" s="6" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="170" x14ac:dyDescent="0.2">
-      <c r="A209" s="6" t="s">
+    <row r="210" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A210" s="6" t="s">
         <v>724</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B210" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="C209" s="6" t="s">
+      <c r="C210" s="6" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="25" t="s">
+    <row r="211" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="25" t="s">
         <v>825</v>
       </c>
-      <c r="B210" s="26" t="s">
+      <c r="B211" s="26" t="s">
         <v>826</v>
       </c>
-      <c r="C210" s="25" t="s">
+      <c r="C211" s="25" t="s">
         <v>824</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A211" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="B211" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="C211" s="6" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="B212" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A213" s="6" t="s">
         <v>880</v>
       </c>
-      <c r="B212" s="17" t="s">
+      <c r="B213" s="17" t="s">
         <v>882</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C213" s="6" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A213" s="6" t="s">
+    <row r="214" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A214" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="B213" s="20" t="s">
+      <c r="B214" s="20" t="s">
         <v>869</v>
       </c>
-      <c r="C213" s="6" t="s">
+      <c r="C214" s="6" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A214" s="6" t="s">
+    <row r="215" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A215" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B215" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C215" s="6" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A215" s="27" t="s">
+    <row r="216" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A216" s="6" t="s">
         <v>888</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B216" s="9" t="s">
         <v>887</v>
       </c>
-      <c r="C215" s="27" t="s">
+      <c r="C216" s="6" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A216" s="6" t="s">
+    <row r="217" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A217" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="B216" s="9" t="s">
+      <c r="B217" s="9" t="s">
         <v>863</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C217" s="6" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A217" s="6" t="s">
+    <row r="218" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A218" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B218" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C218" s="6" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A218" s="6" t="s">
+    <row r="219" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A219" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B219" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="C218" s="6" t="s">
+      <c r="C219" s="6" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A219" s="6" t="s">
+    <row r="220" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A220" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="B219" s="9" t="s">
+      <c r="B220" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="C219" s="6" t="s">
+      <c r="C220" s="6" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="170" x14ac:dyDescent="0.2">
-      <c r="A220" s="6" t="s">
+    <row r="221" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A221" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="B221" s="9" t="s">
         <v>885</v>
       </c>
-      <c r="C220" s="6" t="s">
+      <c r="C221" s="6" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A221" s="6" t="s">
+    <row r="222" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A222" s="6" t="s">
         <v>866</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="B222" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="C221" s="6" t="s">
+      <c r="C222" s="6" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A222" s="22" t="s">
+    <row r="223" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A223" s="22" t="s">
         <v>836</v>
       </c>
-      <c r="B222" s="23" t="s">
+      <c r="B223" s="23" t="s">
         <v>838</v>
       </c>
-      <c r="C222" s="22" t="s">
+      <c r="C223" s="22" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A223" s="6" t="s">
+    <row r="224" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A224" s="6" t="s">
         <v>879</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B224" s="9" t="s">
         <v>877</v>
       </c>
-      <c r="C223" s="6" t="s">
+      <c r="C224" s="6" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A224" s="22" t="s">
+    <row r="225" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A225" s="22" t="s">
         <v>876</v>
       </c>
-      <c r="B224" s="23" t="s">
+      <c r="B225" s="23" t="s">
         <v>874</v>
       </c>
-      <c r="C224" s="22" t="s">
+      <c r="C225" s="22" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A225" s="6" t="s">
+    <row r="226" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A226" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B226" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="C225" s="6" t="s">
+      <c r="C226" s="6" t="s">
         <v>848</v>
       </c>
     </row>
@@ -6172,47 +6189,48 @@
     <hyperlink ref="B177" r:id="rId184" xr:uid="{2062A71F-134B-894B-8846-EBE07862159F}"/>
     <hyperlink ref="B188" r:id="rId185" xr:uid="{160997CC-24EC-AF45-B4B5-A42D9DAF844A}"/>
     <hyperlink ref="B176" r:id="rId186" xr:uid="{25DD0A18-959B-A34B-8A93-D3FEF3FB97F9}"/>
-    <hyperlink ref="B205" r:id="rId187" xr:uid="{BA3D02D1-77B0-BE46-B252-C3907725109A}"/>
-    <hyperlink ref="B208" r:id="rId188" xr:uid="{80CA59D1-9BA2-8346-91A8-5971988A89C5}"/>
-    <hyperlink ref="B195" r:id="rId189" xr:uid="{21B013FC-291F-B645-B9CB-D55C82E0FF3C}"/>
+    <hyperlink ref="B206" r:id="rId187" xr:uid="{BA3D02D1-77B0-BE46-B252-C3907725109A}"/>
+    <hyperlink ref="B209" r:id="rId188" xr:uid="{80CA59D1-9BA2-8346-91A8-5971988A89C5}"/>
+    <hyperlink ref="B196" r:id="rId189" xr:uid="{21B013FC-291F-B645-B9CB-D55C82E0FF3C}"/>
     <hyperlink ref="B189" r:id="rId190" xr:uid="{E1387560-3B21-8744-8282-FA62172ADD59}"/>
     <hyperlink ref="B190" r:id="rId191" xr:uid="{33E26B4B-696D-C148-833C-5E1DE66A42D2}"/>
-    <hyperlink ref="B201" r:id="rId192" xr:uid="{BF1A3EB5-CF92-0841-BAA0-6FB9A8AA212D}"/>
+    <hyperlink ref="B202" r:id="rId192" xr:uid="{BF1A3EB5-CF92-0841-BAA0-6FB9A8AA212D}"/>
     <hyperlink ref="B183" r:id="rId193" xr:uid="{209E1586-B300-E449-AB0D-FB1B05BABBF3}"/>
-    <hyperlink ref="B209" r:id="rId194" xr:uid="{8990349C-86E1-C145-ACEC-0328F8EDB6A4}"/>
-    <hyperlink ref="B200" r:id="rId195" xr:uid="{CAEE1FFD-BED7-0840-8AD6-6D6AA939DF6A}"/>
-    <hyperlink ref="B197" r:id="rId196" xr:uid="{879BD8A7-A4E9-7F46-AF9D-42802A14D7F7}"/>
-    <hyperlink ref="B207" r:id="rId197" xr:uid="{83E9DE22-AF97-714B-8BF6-AA73C186A029}"/>
-    <hyperlink ref="B202" r:id="rId198" xr:uid="{2A9ED378-ECB7-DD40-A541-1DB0EB570B82}"/>
-    <hyperlink ref="B198" r:id="rId199" xr:uid="{E12B1918-0DD5-1C45-AB82-8F12DD0D05A7}"/>
-    <hyperlink ref="B199" r:id="rId200" xr:uid="{E1812E39-EA9E-E44A-8BB6-09A1A913EB25}"/>
-    <hyperlink ref="B196" r:id="rId201" xr:uid="{979A7148-E019-F149-BD01-20370E536B16}"/>
-    <hyperlink ref="B194" r:id="rId202" xr:uid="{58CF6A54-41F2-F24B-9BF6-4B2316313DBF}"/>
-    <hyperlink ref="B203" r:id="rId203" xr:uid="{F3581400-AB2A-0749-A4E4-B5374523CB62}"/>
-    <hyperlink ref="B206" r:id="rId204" xr:uid="{98607997-8D86-1D49-89DC-A94D81C26DE4}"/>
-    <hyperlink ref="B204" r:id="rId205" xr:uid="{5A78EF2F-315D-0248-82E7-3837C642D8EE}"/>
-    <hyperlink ref="B192" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
-    <hyperlink ref="B210" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
-    <hyperlink ref="B214" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
-    <hyperlink ref="B217" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
-    <hyperlink ref="B193" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B222" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
-    <hyperlink ref="B191" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B218" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B225" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B219" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B221" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
-    <hyperlink ref="B216" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
-    <hyperlink ref="B213" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
-    <hyperlink ref="B211" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
-    <hyperlink ref="B224" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
-    <hyperlink ref="B223" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
-    <hyperlink ref="B212" r:id="rId222" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
-    <hyperlink ref="B220" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
-    <hyperlink ref="B215" r:id="rId224" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
+    <hyperlink ref="B210" r:id="rId194" xr:uid="{8990349C-86E1-C145-ACEC-0328F8EDB6A4}"/>
+    <hyperlink ref="B201" r:id="rId195" xr:uid="{CAEE1FFD-BED7-0840-8AD6-6D6AA939DF6A}"/>
+    <hyperlink ref="B198" r:id="rId196" xr:uid="{879BD8A7-A4E9-7F46-AF9D-42802A14D7F7}"/>
+    <hyperlink ref="B208" r:id="rId197" xr:uid="{83E9DE22-AF97-714B-8BF6-AA73C186A029}"/>
+    <hyperlink ref="B203" r:id="rId198" xr:uid="{2A9ED378-ECB7-DD40-A541-1DB0EB570B82}"/>
+    <hyperlink ref="B199" r:id="rId199" xr:uid="{E12B1918-0DD5-1C45-AB82-8F12DD0D05A7}"/>
+    <hyperlink ref="B200" r:id="rId200" xr:uid="{E1812E39-EA9E-E44A-8BB6-09A1A913EB25}"/>
+    <hyperlink ref="B197" r:id="rId201" xr:uid="{979A7148-E019-F149-BD01-20370E536B16}"/>
+    <hyperlink ref="B195" r:id="rId202" xr:uid="{58CF6A54-41F2-F24B-9BF6-4B2316313DBF}"/>
+    <hyperlink ref="B204" r:id="rId203" xr:uid="{F3581400-AB2A-0749-A4E4-B5374523CB62}"/>
+    <hyperlink ref="B207" r:id="rId204" xr:uid="{98607997-8D86-1D49-89DC-A94D81C26DE4}"/>
+    <hyperlink ref="B205" r:id="rId205" xr:uid="{5A78EF2F-315D-0248-82E7-3837C642D8EE}"/>
+    <hyperlink ref="B193" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
+    <hyperlink ref="B211" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
+    <hyperlink ref="B215" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
+    <hyperlink ref="B218" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
+    <hyperlink ref="B194" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
+    <hyperlink ref="B223" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B192" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
+    <hyperlink ref="B219" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B226" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B220" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B222" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B217" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B214" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
+    <hyperlink ref="B212" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
+    <hyperlink ref="B225" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
+    <hyperlink ref="B224" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
+    <hyperlink ref="B213" r:id="rId222" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
+    <hyperlink ref="B221" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
+    <hyperlink ref="B216" r:id="rId224" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
+    <hyperlink ref="B191" r:id="rId225" xr:uid="{FD8B9A55-7C73-9841-A124-F2094F08EAEF}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId225"/>
+  <legacyDrawing r:id="rId226"/>
 </worksheet>
 </file>
 

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730E7546-DA03-4146-8A40-B195F3E6983E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE646A2-0919-614C-B09B-BAA4C0877A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="900">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2792,9 +2792,6 @@
     <t>Ramos, A. L. C. O., Silva, J. E. das M., Ferreira, A. de S., &amp; Lunkes, L. C. (2026). Health locus of control and its relationship with kinesiophobia, disability, and prognosis in chronic low back pain. Brazilian Journal of Pain, 9, e202670. https://doi.org/10.63231/2595-0118.202670-en</t>
   </si>
   <si>
-    <t>Albuquerque, F., Ferreira, A. S., &amp; Lemos, T. (2026). Posturographic assessment of shoulder complex stability in swimmers during Upper-Quarter Y Balance Test: cross-sectional study in young athletes, regarding handedness. Muscles, Ligaments and Tendons Journal, 16. https://doi.org/10.32098/mltj_2026_7106</t>
-  </si>
-  <si>
     <t>10.32098/mltj_2026_7106</t>
   </si>
   <si>
@@ -2826,6 +2823,33 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/12VaPnB9xKA3ooN9KcUKhJYD2hwf3Ikv6</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LyIlUal7_to8FSeG_m_9jg8mSv8zMV4n</t>
+  </si>
+  <si>
+    <t>PainMAP</t>
+  </si>
+  <si>
+    <t>Albuquerque, F., Ferreira, A. S., &amp; Lemos, T. (2026). Posturographic assessment of shoulder complex stability in swimmers during Upper-Quarter Y Balance Test: cross-sectional study in young athletes, regarding handedness. Muscles, Ligaments and Tendons Journal, 16(2). https://doi.org/10.32098/mltj_2026_7106</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/139qDnnp8GKsqTsHP-ytbv5hjJxsoAmR7</t>
+  </si>
+  <si>
+    <t>Ferreira, A. de S., Mota, J. D. H., &amp; Dusek, P. M. (2026). OBSERVATÓRIO: Uma plataforma que interconecta redes de informação. Revista Observatório , 12(1), a01. Recuperado de https://sistemas.uft.edu.br/periodicos/index.php/observatorio/article/view/19601</t>
+  </si>
+  <si>
+    <t>10.20873/uft.2447-4266.2026v12n1a01en</t>
+  </si>
+  <si>
+    <t>10.1038/s41393-026-01238-6</t>
+  </si>
+  <si>
+    <t>Lima, M. A. B., Menezes, K., Xerez, D. R., Côrtes, B. A., Menezes, J. R. L., Holanda, G. S., Silva, A. D., Leite, E. S., Franco, O. B., Faria, M. A. A. M. de, Forte, A. de F., Abreu, L. V., Lichtenberger, R. C. L., Santana, C. F., Rosa, M., Graça-Souza, A. V., Jorge, Á. U. C., Franzoi, A. C., Ferreira, A. S., … Coelho‐Sampaio, T. (2026). Intramedullary injection of polymerized laminin in acute traumatic spinal cord injury: a first-in-human pilot study. Spinal Cord. https://doi.org/10.1038/s41393-026-01238-6</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/150IiTBqdwlZJCOE2Ow1DNwP6pCZvOsKQ</t>
   </si>
 </sst>
 </file>
@@ -3503,7 +3527,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C226"/>
+  <dimension ref="A1:C228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -5604,13 +5628,13 @@
     </row>
     <row r="191" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="C191" s="6" t="s">
         <v>889</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>891</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="170" x14ac:dyDescent="0.2">
@@ -5846,13 +5870,13 @@
     </row>
     <row r="213" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="B213" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="C213" s="6" t="s">
         <v>880</v>
-      </c>
-      <c r="B213" s="17" t="s">
-        <v>882</v>
-      </c>
-      <c r="C213" s="6" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -5879,13 +5903,13 @@
     </row>
     <row r="216" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="153" x14ac:dyDescent="0.2">
@@ -5921,80 +5945,102 @@
         <v>845</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A220" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A221" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="B221" s="9" t="s">
         <v>858</v>
       </c>
-      <c r="C220" s="6" t="s">
+      <c r="C221" s="6" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="170" x14ac:dyDescent="0.2">
-      <c r="A221" s="6" t="s">
+    <row r="222" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A222" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="C222" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="B221" s="9" t="s">
-        <v>885</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A222" s="6" t="s">
+    </row>
+    <row r="223" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="A223" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A224" s="6" t="s">
         <v>866</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="B224" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="C222" s="6" t="s">
+      <c r="C224" s="6" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A223" s="22" t="s">
+    <row r="225" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A225" s="22" t="s">
         <v>836</v>
       </c>
-      <c r="B223" s="23" t="s">
+      <c r="B225" s="23" t="s">
         <v>838</v>
       </c>
-      <c r="C223" s="22" t="s">
+      <c r="C225" s="22" t="s">
         <v>837</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A224" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>877</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A225" s="22" t="s">
-        <v>876</v>
-      </c>
-      <c r="B225" s="23" t="s">
-        <v>874</v>
-      </c>
-      <c r="C225" s="22" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A226" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A227" s="22" t="s">
+        <v>876</v>
+      </c>
+      <c r="B227" s="23" t="s">
+        <v>874</v>
+      </c>
+      <c r="C227" s="22" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A228" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B228" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="C226" s="6" t="s">
+      <c r="C228" s="6" t="s">
         <v>848</v>
       </c>
     </row>
@@ -6213,24 +6259,26 @@
     <hyperlink ref="B215" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
     <hyperlink ref="B218" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B194" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B223" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B225" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B192" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
     <hyperlink ref="B219" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B226" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B220" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B222" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B228" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B221" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B224" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
     <hyperlink ref="B217" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
     <hyperlink ref="B214" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
     <hyperlink ref="B212" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
-    <hyperlink ref="B225" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
-    <hyperlink ref="B224" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
+    <hyperlink ref="B227" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
+    <hyperlink ref="B226" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
     <hyperlink ref="B213" r:id="rId222" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
-    <hyperlink ref="B221" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
+    <hyperlink ref="B222" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
     <hyperlink ref="B216" r:id="rId224" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
     <hyperlink ref="B191" r:id="rId225" xr:uid="{FD8B9A55-7C73-9841-A124-F2094F08EAEF}"/>
+    <hyperlink ref="B220" r:id="rId226" xr:uid="{F2FF60E7-6D7E-E943-807F-C28F2C324FD3}"/>
+    <hyperlink ref="B223" r:id="rId227" xr:uid="{9640ECC6-B685-EC43-A315-F7442ECD1C92}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId226"/>
+  <legacyDrawing r:id="rId228"/>
 </worksheet>
 </file>
 
@@ -6987,7 +7035,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D49A42-744A-EE4A-B294-D2CA066FEF3F}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -7084,6 +7132,14 @@
         <v>786</v>
       </c>
       <c r="C9" s="24"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>891</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7099,6 +7155,7 @@
     <hyperlink ref="B8" r:id="rId10" xr:uid="{23DC5622-B004-494F-9DA9-EEC70BF2FA6F}"/>
     <hyperlink ref="C8" r:id="rId11" xr:uid="{8A1A242A-CEB0-A741-A37D-476362C60252}"/>
     <hyperlink ref="B9" r:id="rId12" xr:uid="{69A58E07-FF33-B141-8778-1C444CD7D4BE}"/>
+    <hyperlink ref="C10" r:id="rId13" xr:uid="{C28E786A-2F85-8D42-9208-5F789C6E5269}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE646A2-0919-614C-B09B-BAA4C0877A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D8E440-48D9-7642-9C29-916D56B6B419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="909">
   <si>
     <t>Doutorado</t>
   </si>
@@ -1610,9 +1610,6 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/14SnDBYYTc-DY2ATCUyTje7A1k_74oZ-c</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zd3dQE-sXaWt409MgiWnXSNl4aawhe60</t>
   </si>
   <si>
     <t>10.3390/healthcare11101386</t>
@@ -2647,9 +2644,6 @@
   </si>
   <si>
     <t>Bonfim, I. S., Nogeuria, L. A. C., Meziat-Filho, N. A., M., Ferreira, A. S., (2025). Factors associated with chronic musculoskeletal pain in individuals with long-COVID after hospital discharge: cross-sectional study. Brazilian Journal of Pain. 8, e202558. https://doi.org/10.63231/2595-0118.202558-en</t>
-  </si>
-  <si>
-    <t>Petrov, I., Stoichev, K., Aliman, O., Kashilska, Y., Gencheva, D., Goranov, G., Tsekoura, D., Parisotto, G., Ferreira, A. S., Lopes, A. J., Dzhafer, N., Bozov, H., Panayotov, K., &amp; Papathanasiou, J. (2025). Effects of differing nutritional supplementation combined with high-intensity aerobic interval training on functional exercise capacity, cardiac function, and quality of life in patients with heart failure and reduced ejection fraction: a randomized trial. American Journal of Physical Medicine &amp;amp; Rehabilitation. https://doi.org/10.1097/phm.0000000000002932</t>
   </si>
   <si>
     <t>10.1097/phm.0000000000002932</t>
@@ -2780,9 +2774,6 @@
     <t>Arulsingh, W., de Sá Ferreira, A., Kandakurti, P.K. et al. C5–C6 and thoracic spine mobilization with postural correction exercise compared with conventional therapy in patients with adhesive capsulitis: a two-group, parallel-arm, single-blinded, randomized clinical trial—study protocol. Trials 27, 378 (2026). https://doi.org/10.1186/s13063-026-09690-8</t>
   </si>
   <si>
-    <t>Ribeiro, R. de S. T., Anjos, F. V. dos, Jesus, I. R. T. de, Monteiro, E. R., &amp; Ferreira, A. de S. (2026). Immediate effects of self-massage compared to static stretching on neuromuscular and functional performance of physically active healthy adults: A crossover study. Journal of Orthopaedic Reports, 101049. https://doi.org/10.1016/j.jorep.2026.101049</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1bvClSoEZjVttegI9SH3ZhPh-NTAwBHqJ</t>
   </si>
   <si>
@@ -2850,6 +2841,42 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/150IiTBqdwlZJCOE2Ow1DNwP6pCZvOsKQ</t>
+  </si>
+  <si>
+    <t>Cassemiro, W. H., Dominski, F. H., de Sá Ferreira, A., &amp; Lunkes, L. C. (2026). Pain and injury prevalence and their associations with psychosocial and motivational factors in amateur beach tennis players: a cross-sectional study. Sport Sciences for Health, 22(3). https://doi.org/10.1007/s11332-026-01895-3</t>
+  </si>
+  <si>
+    <t>10.1007/s11332-026-01895-3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mE3Bj_1xJpc9u2Ys23dprHeDuNaB1zKD</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D0cApCM8RiOrU9QWRL33qIOXw5PuBhQI</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QMKHTNRl_GwmJsEql8Dbdx_KWPbHKgrk</t>
+  </si>
+  <si>
+    <t>10.12688/f1000research.186575.1</t>
+  </si>
+  <si>
+    <t>Hundle PK, Alaparthi GK, Ferreira AdS and Amaravadi SK. Posture and postural balance in people aged 6-39 years with asthma: a systematic review [version 1; peer review: awaiting peer review] F1000Research 2026, 15:1361 https://doi.org/10.12688/f1000research.186575.1</t>
+  </si>
+  <si>
+    <t>Ribeiro, R. de S. T., Anjos, F. V. dos, Jesus, I. R. T. de, Monteiro, E. R., &amp; Ferreira, A. de S. (2026). Immediate effects of self-massage compared to static stretching on neuromuscular and functional performance of physically active healthy adults: A crossover study. Journal of Orthopaedic Reports, 5(4), 101049. https://doi.org/10.1016/j.jorep.2026.101049</t>
+  </si>
+  <si>
+    <t>Petrov, I., Stoichev, K., Aliman, O., Kashilska, Y., Gencheva, D., Goranov, G., Tsekoura, D., Parisotto, G., Sa Ferreira, A., Lopes, A. J., Dzhafer, N., Bozov, H., Panayotov, K., &amp; Papathanasiou, J. (2025). Effects of Differing Nutritional Supplementation Combined With High-Intensity Aerobic Interval Training on Functional Exercise Capacity, Cardiac Function, and Quality of Life in Patients With Heart Failure and Reduced Ejection Fraction. American Journal of Physical Medicine &amp;amp; Rehabilitation, 105(9), 814–822. https://doi.org/10.1097/phm.0000000000002932</t>
+  </si>
+  <si>
+    <t>Certain Curi, A. C., Antunes Ferreira, A. P., Calazans Nogueira, L. A., Filho, N. M., &amp; de Sá Ferreira, A. (2026). Response to the letter regarding “Fatigue in long COVID: An exploratory pragmatic randomized trial of osteopathic care plus physical therapy versus physical therapy alone. International Journal of Osteopathic Medicine, 61, 100858. https://doi.org/10.1016/j.ijosm.2026.100858</t>
+  </si>
+  <si>
+    <t>10.1016/j.ijosm.2026.100858</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nXGc5lEOge5avTjvbtyuii8sTHDoWsc2</t>
   </si>
 </sst>
 </file>
@@ -3453,7 +3480,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>492</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -3527,7 +3554,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A79BD8E-05FA-344E-9159-B54A3FCCEA30}">
-  <dimension ref="A1:C228"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -4055,13 +4082,13 @@
     </row>
     <row r="48" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>510</v>
-      </c>
       <c r="C48" s="16" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -4176,13 +4203,13 @@
     </row>
     <row r="59" spans="1:3" ht="103" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="B59" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>520</v>
-      </c>
       <c r="C59" s="19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="119" x14ac:dyDescent="0.2">
@@ -4198,13 +4225,13 @@
     </row>
     <row r="61" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>513</v>
-      </c>
       <c r="C61" s="16" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -4506,7 +4533,7 @@
     </row>
     <row r="89" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>267</v>
@@ -4858,7 +4885,7 @@
     </row>
     <row r="121" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>362</v>
@@ -4880,7 +4907,7 @@
     </row>
     <row r="123" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>367</v>
@@ -4924,7 +4951,7 @@
     </row>
     <row r="127" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>378</v>
@@ -5155,13 +5182,13 @@
     </row>
     <row r="148" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A148" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B148" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>506</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="119" x14ac:dyDescent="0.2">
@@ -5177,13 +5204,13 @@
     </row>
     <row r="150" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A150" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B150" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="B150" s="9" t="s">
-        <v>529</v>
-      </c>
       <c r="C150" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="153" x14ac:dyDescent="0.2">
@@ -5199,13 +5226,13 @@
     </row>
     <row r="152" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A152" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -5232,18 +5259,18 @@
     </row>
     <row r="155" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A155" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A156" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B156" s="9" t="s">
         <v>485</v>
@@ -5254,18 +5281,18 @@
     </row>
     <row r="157" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B157" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="B157" s="9" t="s">
-        <v>540</v>
-      </c>
       <c r="C157" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A158" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B158" s="9" t="s">
         <v>457</v>
@@ -5298,32 +5325,32 @@
     </row>
     <row r="161" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A161" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A162" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B162" s="9" t="s">
         <v>474</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A163" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B163" s="9" t="s">
         <v>525</v>
-      </c>
-      <c r="B163" s="9" t="s">
-        <v>526</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>415</v>
@@ -5331,13 +5358,13 @@
     </row>
     <row r="164" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A164" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="B164" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B164" s="9" t="s">
-        <v>495</v>
-      </c>
       <c r="C164" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="119" x14ac:dyDescent="0.2">
@@ -5375,24 +5402,24 @@
     </row>
     <row r="168" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A168" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -5408,10 +5435,10 @@
     </row>
     <row r="171" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="B171" s="18" t="s">
         <v>501</v>
-      </c>
-      <c r="B171" s="18" t="s">
-        <v>502</v>
       </c>
       <c r="C171" s="14" t="s">
         <v>440</v>
@@ -5419,633 +5446,666 @@
     </row>
     <row r="172" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A172" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B172" s="20" t="s">
         <v>573</v>
       </c>
-      <c r="B172" s="20" t="s">
-        <v>574</v>
-      </c>
       <c r="C172" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A173" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="B173" s="20" t="s">
         <v>657</v>
       </c>
-      <c r="B173" s="20" t="s">
-        <v>658</v>
-      </c>
       <c r="C173" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A174" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B174" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="C174" s="6" t="s">
         <v>565</v>
-      </c>
-      <c r="B174" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A175" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A176" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="B176" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="B176" s="20" t="s">
-        <v>673</v>
-      </c>
       <c r="C176" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A177" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="C177" s="6" t="s">
         <v>665</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>667</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A178" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A179" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A180" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B180" s="7" t="s">
         <v>660</v>
       </c>
-      <c r="B180" s="7" t="s">
-        <v>661</v>
-      </c>
       <c r="C180" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A181" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B181" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="B181" s="9" t="s">
-        <v>581</v>
-      </c>
       <c r="C181" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A182" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="204" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="B183" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>710</v>
-      </c>
       <c r="C183" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A184" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B184" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="B184" s="9" t="s">
-        <v>664</v>
-      </c>
       <c r="C184" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A185" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B185" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="B185" s="9" t="s">
-        <v>564</v>
-      </c>
       <c r="C185" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A186" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="C186" s="6" t="s">
         <v>545</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="C186" s="6" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A187" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B187" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="B187" s="9" t="s">
-        <v>543</v>
-      </c>
       <c r="C187" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A188" s="14" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B188" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C188" s="14" t="s">
         <v>668</v>
-      </c>
-      <c r="C188" s="14" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="B189" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="B189" s="7" t="s">
-        <v>697</v>
-      </c>
       <c r="C189" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A190" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="C190" s="6" t="s">
         <v>698</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="C190" s="6" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B193" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="C193" s="6" t="s">
         <v>820</v>
-      </c>
-      <c r="C193" s="6" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B194" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="C194" s="6" t="s">
         <v>833</v>
-      </c>
-      <c r="C194" s="6" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B195" s="7" t="s">
         <v>748</v>
       </c>
-      <c r="B195" s="7" t="s">
-        <v>749</v>
-      </c>
       <c r="C195" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B197" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="C197" s="6" t="s">
         <v>742</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A198" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="C198" s="6" t="s">
         <v>728</v>
-      </c>
-      <c r="B198" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="C198" s="6" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A201" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B203" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="B203" s="9" t="s">
-        <v>735</v>
-      </c>
       <c r="C203" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="B204" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="B204" s="9" t="s">
-        <v>752</v>
-      </c>
       <c r="C204" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B205" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="C205" s="6" t="s">
         <v>759</v>
-      </c>
-      <c r="C205" s="6" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A207" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B207" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="B207" s="9" t="s">
-        <v>758</v>
-      </c>
       <c r="C207" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A208" s="6" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A209" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A210" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A211" s="25" t="s">
+        <v>824</v>
+      </c>
+      <c r="B211" s="26" t="s">
         <v>825</v>
       </c>
-      <c r="B211" s="26" t="s">
-        <v>826</v>
-      </c>
       <c r="C211" s="25" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="B212" s="17" t="s">
         <v>870</v>
       </c>
-      <c r="B212" s="17" t="s">
-        <v>872</v>
-      </c>
       <c r="C212" s="6" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A215" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="B215" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="B215" s="7" t="s">
-        <v>829</v>
-      </c>
       <c r="C215" s="6" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A217" s="6" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="B217" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A218" s="6" t="s">
         <v>863</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="B218" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A219" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A220" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A221" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A222" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A223" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A224" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A225" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="A226" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A227" s="6" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A218" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A219" s="6" t="s">
+      <c r="B227" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="C227" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="B219" s="9" t="s">
+    </row>
+    <row r="228" spans="1:3" ht="221" x14ac:dyDescent="0.2">
+      <c r="A228" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A229" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A230" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A231" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C231" s="6" t="s">
         <v>846</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A220" s="6" t="s">
-        <v>895</v>
-      </c>
-      <c r="B220" s="9" t="s">
-        <v>894</v>
-      </c>
-      <c r="C220" s="6" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A221" s="6" t="s">
-        <v>856</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>858</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="170" x14ac:dyDescent="0.2">
-      <c r="A222" s="6" t="s">
-        <v>882</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>884</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" ht="187" x14ac:dyDescent="0.2">
-      <c r="A223" s="6" t="s">
-        <v>898</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>899</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A224" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>862</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A225" s="22" t="s">
-        <v>836</v>
-      </c>
-      <c r="B225" s="23" t="s">
-        <v>838</v>
-      </c>
-      <c r="C225" s="22" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A226" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="B226" s="9" t="s">
-        <v>877</v>
-      </c>
-      <c r="C226" s="6" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="136" x14ac:dyDescent="0.2">
-      <c r="A227" s="22" t="s">
-        <v>876</v>
-      </c>
-      <c r="B227" s="23" t="s">
-        <v>874</v>
-      </c>
-      <c r="C227" s="22" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A228" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="B228" s="7" t="s">
-        <v>849</v>
-      </c>
-      <c r="C228" s="6" t="s">
-        <v>848</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C189:C1048576 C1:C187">
+  <conditionalFormatting sqref="C1:C187 C189:C1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
@@ -6257,28 +6317,31 @@
     <hyperlink ref="B193" r:id="rId206" xr:uid="{2CC9FDA5-1399-844B-A10A-621ACD4E3D83}"/>
     <hyperlink ref="B211" r:id="rId207" xr:uid="{FAB36EE3-F2EB-2946-BC17-D6D53846E0A0}"/>
     <hyperlink ref="B215" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
-    <hyperlink ref="B218" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
+    <hyperlink ref="B220" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B194" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B225" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
+    <hyperlink ref="B228" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
     <hyperlink ref="B192" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B219" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B228" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B221" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B224" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
-    <hyperlink ref="B217" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B221" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B231" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B224" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B227" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B218" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
     <hyperlink ref="B214" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
     <hyperlink ref="B212" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
-    <hyperlink ref="B227" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
-    <hyperlink ref="B226" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
+    <hyperlink ref="B230" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
+    <hyperlink ref="B229" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
     <hyperlink ref="B213" r:id="rId222" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
-    <hyperlink ref="B222" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
+    <hyperlink ref="B225" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
     <hyperlink ref="B216" r:id="rId224" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
     <hyperlink ref="B191" r:id="rId225" xr:uid="{FD8B9A55-7C73-9841-A124-F2094F08EAEF}"/>
-    <hyperlink ref="B220" r:id="rId226" xr:uid="{F2FF60E7-6D7E-E943-807F-C28F2C324FD3}"/>
-    <hyperlink ref="B223" r:id="rId227" xr:uid="{9640ECC6-B685-EC43-A315-F7442ECD1C92}"/>
+    <hyperlink ref="B222" r:id="rId226" xr:uid="{F2FF60E7-6D7E-E943-807F-C28F2C324FD3}"/>
+    <hyperlink ref="B226" r:id="rId227" xr:uid="{9640ECC6-B685-EC43-A315-F7442ECD1C92}"/>
+    <hyperlink ref="B217" r:id="rId228" xr:uid="{CC131DE1-D6BE-5E48-AC48-287482CBE982}"/>
+    <hyperlink ref="B223" r:id="rId229" xr:uid="{21E33509-C69E-9C4B-BD46-34A01A62BAB0}"/>
+    <hyperlink ref="B219" r:id="rId230" xr:uid="{CF60C9D8-AC76-CA42-986C-91E7F2B11DC1}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId228"/>
+  <legacyDrawing r:id="rId231"/>
 </worksheet>
 </file>
 
@@ -6306,68 +6369,68 @@
     </row>
     <row r="2" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>688</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="256" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>686</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>687</v>
-      </c>
       <c r="C3" s="12" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>703</v>
-      </c>
       <c r="C4" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="14" customFormat="1" ht="154" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>784</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -6411,35 +6474,35 @@
     </row>
     <row r="2" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>682</v>
-      </c>
       <c r="C2" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>753</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -6515,75 +6578,75 @@
     </row>
     <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>548</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>550</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>717</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -6630,360 +6693,360 @@
     </row>
     <row r="2" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="86" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>584</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>585</v>
       </c>
       <c r="C3" s="14"/>
     </row>
     <row r="4" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>587</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>588</v>
-      </c>
       <c r="C4" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="171" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>593</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>595</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="103" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>600</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>601</v>
       </c>
       <c r="C10" s="14"/>
     </row>
     <row r="11" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="137" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>718</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>720</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="154" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A34" s="22" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -7049,7 +7112,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
@@ -7085,7 +7148,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -7093,52 +7156,52 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>726</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>785</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>786</v>
       </c>
       <c r="C9" s="24"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
     </row>
   </sheetData>
@@ -7185,123 +7248,123 @@
     </row>
     <row r="2" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>787</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>790</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>791</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>794</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>796</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>797</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>799</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>800</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>803</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>805</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>806</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>808</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>809</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>812</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>815</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>818</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>819</v>
       </c>
     </row>
   </sheetData>
